--- a/01-artefactos-de-gestao/01.06-avaliacao-interna-do-grupo/m2-mapa-carga-planeada-v01.xlsx
+++ b/01-artefactos-de-gestao/01.06-avaliacao-interna-do-grupo/m2-mapa-carga-planeada-v01.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ipppt.sharepoint.com/teams/LEI-GrupodeLDS-UTPORTO/Documentos Partilhados/Para M2/Gestão/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ipppt.sharepoint.com/teams/LEI-GrupodeLDS-UTPORTO/Documentos Partilhados/projeto/01-artefactos-de-gestao/01.06-avaliacao-interna-do-grupo/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="253" documentId="13_ncr:1_{36D489DA-0E1E-4AAB-A288-D8B9E481960E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1B17431A-9C2C-4B69-89A7-455B924E41A1}"/>
+  <xr:revisionPtr revIDLastSave="257" documentId="13_ncr:1_{36D489DA-0E1E-4AAB-A288-D8B9E481960E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0C810873-E560-4E71-AF03-410D895BB471}"/>
   <bookViews>
-    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="13056" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="16305" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Mapa de Carga Planeada" sheetId="1" r:id="rId1"/>
@@ -839,12 +839,6 @@
     <t>/projeto/01-artefactos-de-gestao/01.04-backlog-de-projeto/m2-s02-sprint-backlog-v01.xlsx</t>
   </si>
   <si>
-    <t>/projeto/01-artefactos-de-gestao/01.03-reunioes-de-grupo/m1-20260919-s01-sprint-backlog-v01.pdf</t>
-  </si>
-  <si>
-    <t>/projeto/01-artefactos-de-gestao/01.03-reunioes-de-grupo/m2-20261002-s02-sprint-backlog-v01.pdf</t>
-  </si>
-  <si>
     <t>Atualizar Grelha de Rotação de Papéis</t>
   </si>
   <si>
@@ -885,6 +879,12 @@
   </si>
   <si>
     <t>/projeto/01-artefactos-de-gestao/01.03-reunioes-de-grupo/01.03.03-reunioes-de-sprint-planning/01.03.03.02-atas/m2-20261002-ata-sprint-planning-v01.pdf</t>
+  </si>
+  <si>
+    <t>/projeto/01-artefactos-de-gestao/01.04-backlog-de-projeto/m2-s02-20261007-sprint-backlog-v01.pdf</t>
+  </si>
+  <si>
+    <t>/projeto/01-artefactos-de-gestao/01.04-backlog-de-projeto/m1-20260919-s01-sprint-backlog-v01.pdf</t>
   </si>
 </sst>
 </file>
@@ -1476,10 +1476,10 @@
       <sheetName val="Listas de apoio"/>
     </sheetNames>
     <sheetDataSet>
-      <sheetData sheetId="0" refreshError="1"/>
-      <sheetData sheetId="1" refreshError="1"/>
-      <sheetData sheetId="2" refreshError="1"/>
-      <sheetData sheetId="3" refreshError="1"/>
+      <sheetData sheetId="0"/>
+      <sheetData sheetId="1"/>
+      <sheetData sheetId="2"/>
+      <sheetData sheetId="3"/>
       <sheetData sheetId="4">
         <row r="5">
           <cell r="A5">
@@ -1716,7 +1716,7 @@
     <tabColor rgb="FF1F4E78"/>
   </sheetPr>
   <dimension ref="A1:Z193"/>
-  <sheetFormatPr defaultRowHeight="13.8"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="19" customWidth="1"/>
     <col min="2" max="5" width="17" customWidth="1"/>
@@ -1847,7 +1847,7 @@
       <c r="Y4" s="1"/>
       <c r="Z4" s="1"/>
     </row>
-    <row r="5" spans="1:26" ht="21.9" customHeight="1">
+    <row r="5" spans="1:26" ht="21.95" customHeight="1">
       <c r="A5" s="23" t="s">
         <v>4</v>
       </c>
@@ -2036,7 +2036,7 @@
       <c r="Y10" s="1"/>
       <c r="Z10" s="1"/>
     </row>
-    <row r="11" spans="1:26" ht="21.9" customHeight="1">
+    <row r="11" spans="1:26" ht="21.95" customHeight="1">
       <c r="A11" s="23" t="s">
         <v>10</v>
       </c>
@@ -2106,7 +2106,7 @@
       <c r="Y12" s="1"/>
       <c r="Z12" s="1"/>
     </row>
-    <row r="13" spans="1:26" ht="22.8">
+    <row r="13" spans="1:26" ht="24">
       <c r="A13" s="3" t="str">
         <f>IF('Listas de apoio'!G5="","",'Listas de apoio'!G5)</f>
         <v>André Filipe Moreira Mesquita</v>
@@ -2152,7 +2152,7 @@
       <c r="Y13" s="1"/>
       <c r="Z13" s="1"/>
     </row>
-    <row r="14" spans="1:26" ht="22.8">
+    <row r="14" spans="1:26" ht="24">
       <c r="A14" s="3" t="str">
         <f>IF('Listas de apoio'!G6="","",'Listas de apoio'!G6)</f>
         <v>Gonçalo Dinis Magalhães Teixeira</v>
@@ -2198,7 +2198,7 @@
       <c r="Y14" s="1"/>
       <c r="Z14" s="1"/>
     </row>
-    <row r="15" spans="1:26">
+    <row r="15" spans="1:26" ht="24">
       <c r="A15" s="3" t="str">
         <f>IF('Listas de apoio'!G7="","",'Listas de apoio'!G7)</f>
         <v>Gonçalo Magalhães Ribeiro</v>
@@ -2244,7 +2244,7 @@
       <c r="Y15" s="1"/>
       <c r="Z15" s="1"/>
     </row>
-    <row r="16" spans="1:26">
+    <row r="16" spans="1:26" ht="24">
       <c r="A16" s="3" t="str">
         <f>IF('Listas de apoio'!G8="","",'Listas de apoio'!G8)</f>
         <v>Ivan Cristiano Silva Mendes</v>
@@ -2363,7 +2363,7 @@
       <c r="Y18" s="1"/>
       <c r="Z18" s="1"/>
     </row>
-    <row r="19" spans="1:26" ht="21.9" customHeight="1">
+    <row r="19" spans="1:26" ht="21.95" customHeight="1">
       <c r="A19" s="23" t="s">
         <v>18</v>
       </c>
@@ -2651,7 +2651,7 @@
       <c r="Y27" s="1"/>
       <c r="Z27" s="1"/>
     </row>
-    <row r="28" spans="1:26" ht="21.9" customHeight="1">
+    <row r="28" spans="1:26" ht="21.95" customHeight="1">
       <c r="A28" s="23" t="s">
         <v>27</v>
       </c>
@@ -7825,17 +7825,17 @@
     <tabColor rgb="FF5B9BD5"/>
   </sheetPr>
   <dimension ref="A1:Z193"/>
-  <sheetFormatPr defaultRowHeight="13.8"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
-    <col min="2" max="2" width="30.19921875" customWidth="1"/>
+    <col min="2" max="2" width="30.25" customWidth="1"/>
     <col min="3" max="3" width="42" customWidth="1"/>
     <col min="4" max="4" width="18" customWidth="1"/>
-    <col min="5" max="5" width="29.3984375" customWidth="1"/>
+    <col min="5" max="5" width="29.375" customWidth="1"/>
     <col min="6" max="6" width="11" customWidth="1"/>
-    <col min="7" max="7" width="28.09765625" customWidth="1"/>
+    <col min="7" max="7" width="28.125" customWidth="1"/>
     <col min="8" max="8" width="11" customWidth="1"/>
-    <col min="9" max="9" width="29.3984375" customWidth="1"/>
+    <col min="9" max="9" width="29.375" customWidth="1"/>
     <col min="10" max="10" width="11" customWidth="1"/>
   </cols>
   <sheetData>
@@ -7961,7 +7961,7 @@
       <c r="Y4" s="1"/>
       <c r="Z4" s="1"/>
     </row>
-    <row r="5" spans="1:26" ht="21.9" customHeight="1">
+    <row r="5" spans="1:26" ht="21.95" customHeight="1">
       <c r="A5" s="23" t="s">
         <v>36</v>
       </c>
@@ -8025,7 +8025,7 @@
       <c r="Y6" s="1"/>
       <c r="Z6" s="1"/>
     </row>
-    <row r="7" spans="1:26" ht="16.8" customHeight="1">
+    <row r="7" spans="1:26" ht="16.899999999999999" customHeight="1">
       <c r="A7" s="4" t="s">
         <v>155</v>
       </c>
@@ -8681,7 +8681,7 @@
       <c r="Y27" s="1"/>
       <c r="Z27" s="1"/>
     </row>
-    <row r="28" spans="1:26" ht="21.9" customHeight="1">
+    <row r="28" spans="1:26" ht="21.95" customHeight="1">
       <c r="A28" s="23" t="s">
         <v>41</v>
       </c>
@@ -8711,7 +8711,7 @@
       <c r="Y28" s="1"/>
       <c r="Z28" s="1"/>
     </row>
-    <row r="29" spans="1:26" ht="39.9" customHeight="1">
+    <row r="29" spans="1:26" ht="39.950000000000003" customHeight="1">
       <c r="A29" s="2" t="s">
         <v>28</v>
       </c>
@@ -8757,7 +8757,7 @@
       <c r="C30" s="29"/>
       <c r="D30" s="29"/>
       <c r="E30" s="29" t="s">
-        <v>256</v>
+        <v>271</v>
       </c>
       <c r="F30" s="29"/>
       <c r="G30" s="29"/>
@@ -8793,12 +8793,12 @@
       <c r="C31" s="29"/>
       <c r="D31" s="29"/>
       <c r="E31" s="29" t="s">
-        <v>257</v>
+        <v>270</v>
       </c>
       <c r="F31" s="29"/>
       <c r="G31" s="29"/>
       <c r="H31" s="29" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="I31" s="29"/>
       <c r="J31" s="29"/>
@@ -9351,7 +9351,7 @@
       <c r="Y50" s="1"/>
       <c r="Z50" s="1"/>
     </row>
-    <row r="51" spans="1:26" ht="21.9" customHeight="1">
+    <row r="51" spans="1:26" ht="21.95" customHeight="1">
       <c r="A51" s="23" t="s">
         <v>44</v>
       </c>
@@ -9976,7 +9976,7 @@
         <v>242</v>
       </c>
       <c r="C64" s="18" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="D64" s="20">
         <v>10</v>
@@ -10078,7 +10078,7 @@
         <v>244</v>
       </c>
       <c r="C66" s="18" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="D66" s="20">
         <v>30</v>
@@ -10129,7 +10129,7 @@
         <v>245</v>
       </c>
       <c r="C67" s="18" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="D67" s="20">
         <v>30</v>
@@ -10231,7 +10231,7 @@
         <v>247</v>
       </c>
       <c r="C69" s="18" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D69" s="20">
         <v>50</v>
@@ -10384,7 +10384,7 @@
         <v>250</v>
       </c>
       <c r="C72" s="18" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="D72" s="20">
         <v>50</v>
@@ -10432,10 +10432,10 @@
         <v>157</v>
       </c>
       <c r="B73" s="18" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="C73" s="18" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D73" s="20">
         <v>30</v>
@@ -10483,10 +10483,10 @@
         <v>157</v>
       </c>
       <c r="B74" s="18" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="C74" s="19" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="D74" s="20">
         <v>30</v>
@@ -10534,10 +10534,10 @@
         <v>157</v>
       </c>
       <c r="B75" s="18" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="C75" s="19" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="D75" s="20">
         <v>20</v>
@@ -10585,10 +10585,10 @@
         <v>157</v>
       </c>
       <c r="B76" s="18" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="C76" s="18" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="D76" s="20">
         <v>20</v>
@@ -14676,7 +14676,7 @@
     <tabColor rgb="FFA5A5A5"/>
   </sheetPr>
   <dimension ref="A1:Z200"/>
-  <sheetFormatPr defaultRowHeight="13.8"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="43" customWidth="1"/>
     <col min="2" max="2" width="16" customWidth="1"/>
@@ -14808,7 +14808,7 @@
       <c r="Y4" s="1"/>
       <c r="Z4" s="1"/>
     </row>
-    <row r="5" spans="1:26" ht="33.9" customHeight="1">
+    <row r="5" spans="1:26" ht="33.950000000000003" customHeight="1">
       <c r="A5" s="3" t="s">
         <v>60</v>
       </c>
@@ -14845,7 +14845,7 @@
       <c r="Y5" s="1"/>
       <c r="Z5" s="1"/>
     </row>
-    <row r="6" spans="1:26" ht="33.9" customHeight="1">
+    <row r="6" spans="1:26" ht="33.950000000000003" customHeight="1">
       <c r="A6" s="3" t="s">
         <v>63</v>
       </c>
@@ -14882,7 +14882,7 @@
       <c r="Y6" s="1"/>
       <c r="Z6" s="1"/>
     </row>
-    <row r="7" spans="1:26" ht="33.9" customHeight="1">
+    <row r="7" spans="1:26" ht="33.950000000000003" customHeight="1">
       <c r="A7" s="3" t="s">
         <v>65</v>
       </c>
@@ -14919,7 +14919,7 @@
       <c r="Y7" s="1"/>
       <c r="Z7" s="1"/>
     </row>
-    <row r="8" spans="1:26" ht="33.9" customHeight="1">
+    <row r="8" spans="1:26" ht="33.950000000000003" customHeight="1">
       <c r="A8" s="3" t="s">
         <v>67</v>
       </c>
@@ -14957,7 +14957,7 @@
       <c r="Y8" s="1"/>
       <c r="Z8" s="1"/>
     </row>
-    <row r="9" spans="1:26" ht="33.9" customHeight="1">
+    <row r="9" spans="1:26" ht="33.950000000000003" customHeight="1">
       <c r="A9" s="3" t="s">
         <v>69</v>
       </c>
@@ -14995,7 +14995,7 @@
       <c r="Y9" s="1"/>
       <c r="Z9" s="1"/>
     </row>
-    <row r="10" spans="1:26" ht="33.9" customHeight="1">
+    <row r="10" spans="1:26" ht="33.950000000000003" customHeight="1">
       <c r="A10" s="3" t="s">
         <v>208</v>
       </c>
@@ -15033,7 +15033,7 @@
       <c r="Y10" s="1"/>
       <c r="Z10" s="1"/>
     </row>
-    <row r="11" spans="1:26" ht="33.9" customHeight="1">
+    <row r="11" spans="1:26" ht="33.950000000000003" customHeight="1">
       <c r="A11" s="3" t="s">
         <v>72</v>
       </c>
@@ -15071,7 +15071,7 @@
       <c r="Y11" s="1"/>
       <c r="Z11" s="1"/>
     </row>
-    <row r="12" spans="1:26" ht="33.9" customHeight="1">
+    <row r="12" spans="1:26" ht="33.950000000000003" customHeight="1">
       <c r="A12" s="3" t="s">
         <v>74</v>
       </c>
@@ -15109,7 +15109,7 @@
       <c r="Y12" s="1"/>
       <c r="Z12" s="1"/>
     </row>
-    <row r="13" spans="1:26" ht="33.9" customHeight="1">
+    <row r="13" spans="1:26" ht="33.950000000000003" customHeight="1">
       <c r="A13" s="3" t="s">
         <v>76</v>
       </c>
@@ -15147,7 +15147,7 @@
       <c r="Y13" s="1"/>
       <c r="Z13" s="1"/>
     </row>
-    <row r="14" spans="1:26" ht="33.9" customHeight="1">
+    <row r="14" spans="1:26" ht="33.950000000000003" customHeight="1">
       <c r="A14" s="3" t="s">
         <v>78</v>
       </c>
@@ -15185,7 +15185,7 @@
       <c r="Y14" s="1"/>
       <c r="Z14" s="1"/>
     </row>
-    <row r="15" spans="1:26" ht="33.9" customHeight="1">
+    <row r="15" spans="1:26" ht="33.950000000000003" customHeight="1">
       <c r="A15" s="3" t="s">
         <v>80</v>
       </c>
@@ -15223,7 +15223,7 @@
       <c r="Y15" s="1"/>
       <c r="Z15" s="1"/>
     </row>
-    <row r="16" spans="1:26" ht="33.9" customHeight="1">
+    <row r="16" spans="1:26" ht="33.950000000000003" customHeight="1">
       <c r="A16" s="3" t="s">
         <v>187</v>
       </c>
@@ -15261,7 +15261,7 @@
       <c r="Y16" s="1"/>
       <c r="Z16" s="1"/>
     </row>
-    <row r="17" spans="1:26" ht="33.9" customHeight="1">
+    <row r="17" spans="1:26" ht="33.950000000000003" customHeight="1">
       <c r="A17" s="3" t="s">
         <v>82</v>
       </c>
@@ -15299,7 +15299,7 @@
       <c r="Y17" s="1"/>
       <c r="Z17" s="1"/>
     </row>
-    <row r="18" spans="1:26" ht="33.9" customHeight="1">
+    <row r="18" spans="1:26" ht="33.950000000000003" customHeight="1">
       <c r="A18" s="3" t="s">
         <v>84</v>
       </c>
@@ -15337,7 +15337,7 @@
       <c r="Y18" s="1"/>
       <c r="Z18" s="1"/>
     </row>
-    <row r="19" spans="1:26" ht="33.9" customHeight="1">
+    <row r="19" spans="1:26" ht="33.950000000000003" customHeight="1">
       <c r="A19" s="3" t="s">
         <v>86</v>
       </c>
@@ -15375,7 +15375,7 @@
       <c r="Y19" s="1"/>
       <c r="Z19" s="1"/>
     </row>
-    <row r="20" spans="1:26" ht="33.9" customHeight="1">
+    <row r="20" spans="1:26" ht="33.950000000000003" customHeight="1">
       <c r="A20" s="3" t="s">
         <v>88</v>
       </c>
@@ -15413,7 +15413,7 @@
       <c r="Y20" s="1"/>
       <c r="Z20" s="1"/>
     </row>
-    <row r="21" spans="1:26" ht="33.9" customHeight="1">
+    <row r="21" spans="1:26" ht="33.950000000000003" customHeight="1">
       <c r="A21" s="3" t="s">
         <v>189</v>
       </c>
@@ -15451,7 +15451,7 @@
       <c r="Y21" s="1"/>
       <c r="Z21" s="1"/>
     </row>
-    <row r="22" spans="1:26" ht="33.9" customHeight="1">
+    <row r="22" spans="1:26" ht="33.950000000000003" customHeight="1">
       <c r="A22" s="3" t="s">
         <v>191</v>
       </c>
@@ -15489,7 +15489,7 @@
       <c r="Y22" s="1"/>
       <c r="Z22" s="1"/>
     </row>
-    <row r="23" spans="1:26" ht="33.9" customHeight="1">
+    <row r="23" spans="1:26" ht="33.950000000000003" customHeight="1">
       <c r="A23" s="3" t="s">
         <v>193</v>
       </c>
@@ -15527,7 +15527,7 @@
       <c r="Y23" s="1"/>
       <c r="Z23" s="1"/>
     </row>
-    <row r="24" spans="1:26" ht="33.9" customHeight="1">
+    <row r="24" spans="1:26" ht="33.950000000000003" customHeight="1">
       <c r="A24" s="3" t="s">
         <v>195</v>
       </c>
@@ -15565,7 +15565,7 @@
       <c r="Y24" s="1"/>
       <c r="Z24" s="1"/>
     </row>
-    <row r="25" spans="1:26" ht="33.9" customHeight="1">
+    <row r="25" spans="1:26" ht="33.950000000000003" customHeight="1">
       <c r="A25" s="3" t="s">
         <v>197</v>
       </c>
@@ -15603,7 +15603,7 @@
       <c r="Y25" s="1"/>
       <c r="Z25" s="1"/>
     </row>
-    <row r="26" spans="1:26" ht="33.9" customHeight="1">
+    <row r="26" spans="1:26" ht="33.950000000000003" customHeight="1">
       <c r="A26" s="3" t="s">
         <v>198</v>
       </c>
@@ -15641,7 +15641,7 @@
       <c r="Y26" s="1"/>
       <c r="Z26" s="1"/>
     </row>
-    <row r="27" spans="1:26" ht="33.9" customHeight="1">
+    <row r="27" spans="1:26" ht="33.950000000000003" customHeight="1">
       <c r="A27" s="3" t="s">
         <v>200</v>
       </c>
@@ -15679,7 +15679,7 @@
       <c r="Y27" s="1"/>
       <c r="Z27" s="1"/>
     </row>
-    <row r="28" spans="1:26" ht="33.9" customHeight="1">
+    <row r="28" spans="1:26" ht="33.950000000000003" customHeight="1">
       <c r="A28" s="3" t="s">
         <v>202</v>
       </c>
@@ -15717,7 +15717,7 @@
       <c r="Y28" s="1"/>
       <c r="Z28" s="1"/>
     </row>
-    <row r="29" spans="1:26" ht="33.9" customHeight="1">
+    <row r="29" spans="1:26" ht="33.950000000000003" customHeight="1">
       <c r="A29" s="3" t="s">
         <v>90</v>
       </c>
@@ -15755,7 +15755,7 @@
       <c r="Y29" s="1"/>
       <c r="Z29" s="1"/>
     </row>
-    <row r="30" spans="1:26" ht="33.9" customHeight="1">
+    <row r="30" spans="1:26" ht="33.950000000000003" customHeight="1">
       <c r="A30" s="3" t="s">
         <v>92</v>
       </c>
@@ -20573,7 +20573,7 @@
     <tabColor rgb="FF70AD47"/>
   </sheetPr>
   <dimension ref="A1:Z200"/>
-  <sheetFormatPr defaultRowHeight="13.8"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
     <col min="2" max="2" width="27" customWidth="1"/>
@@ -20677,7 +20677,7 @@
       <c r="Y3" s="1"/>
       <c r="Z3" s="1"/>
     </row>
-    <row r="4" spans="1:26" ht="57">
+    <row r="4" spans="1:26" ht="60">
       <c r="A4" s="3">
         <v>1</v>
       </c>
@@ -21101,7 +21101,7 @@
       <c r="Y15" s="1"/>
       <c r="Z15" s="1"/>
     </row>
-    <row r="16" spans="1:26" ht="21.9" customHeight="1">
+    <row r="16" spans="1:26" ht="21.95" customHeight="1">
       <c r="A16" s="23" t="s">
         <v>128</v>
       </c>
@@ -26349,7 +26349,7 @@
     <tabColor rgb="FFA5A5A5"/>
   </sheetPr>
   <dimension ref="A1:Z200"/>
-  <sheetFormatPr defaultRowHeight="13.8"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="19" customWidth="1"/>
     <col min="2" max="2" width="3" customWidth="1"/>
@@ -26491,7 +26491,7 @@
       <c r="Y4" s="1"/>
       <c r="Z4" s="1"/>
     </row>
-    <row r="5" spans="1:26" ht="22.8">
+    <row r="5" spans="1:26" ht="24">
       <c r="A5" s="3">
         <v>10</v>
       </c>
@@ -26531,7 +26531,7 @@
       <c r="Y5" s="1"/>
       <c r="Z5" s="1"/>
     </row>
-    <row r="6" spans="1:26" ht="22.8">
+    <row r="6" spans="1:26" ht="24">
       <c r="A6" s="3">
         <v>20</v>
       </c>
@@ -26571,7 +26571,7 @@
       <c r="Y6" s="1"/>
       <c r="Z6" s="1"/>
     </row>
-    <row r="7" spans="1:26" ht="22.8">
+    <row r="7" spans="1:26" ht="24">
       <c r="A7" s="3">
         <v>30</v>
       </c>
@@ -26611,7 +26611,7 @@
       <c r="Y7" s="1"/>
       <c r="Z7" s="1"/>
     </row>
-    <row r="8" spans="1:26" ht="22.8">
+    <row r="8" spans="1:26" ht="24">
       <c r="A8" s="3">
         <v>50</v>
       </c>
@@ -27165,7 +27165,7 @@
       <c r="Y25" s="1"/>
       <c r="Z25" s="1"/>
     </row>
-    <row r="26" spans="1:26" ht="21.9" customHeight="1">
+    <row r="26" spans="1:26" ht="21.95" customHeight="1">
       <c r="A26" s="23" t="s">
         <v>178</v>
       </c>
@@ -27195,7 +27195,7 @@
       <c r="Y26" s="1"/>
       <c r="Z26" s="1"/>
     </row>
-    <row r="27" spans="1:26" ht="33.9" customHeight="1">
+    <row r="27" spans="1:26" ht="33.950000000000003" customHeight="1">
       <c r="A27" s="8" t="s">
         <v>151</v>
       </c>
@@ -27227,7 +27227,7 @@
       <c r="Y27" s="1"/>
       <c r="Z27" s="1"/>
     </row>
-    <row r="28" spans="1:26" ht="33.9" customHeight="1">
+    <row r="28" spans="1:26" ht="33.950000000000003" customHeight="1">
       <c r="A28" s="8" t="s">
         <v>179</v>
       </c>
@@ -27259,7 +27259,7 @@
       <c r="Y28" s="1"/>
       <c r="Z28" s="1"/>
     </row>
-    <row r="29" spans="1:26" ht="33.9" customHeight="1">
+    <row r="29" spans="1:26" ht="33.950000000000003" customHeight="1">
       <c r="A29" s="8" t="s">
         <v>181</v>
       </c>
@@ -27291,7 +27291,7 @@
       <c r="Y29" s="1"/>
       <c r="Z29" s="1"/>
     </row>
-    <row r="30" spans="1:26" ht="33.9" customHeight="1">
+    <row r="30" spans="1:26" ht="33.950000000000003" customHeight="1">
       <c r="A30" s="8" t="s">
         <v>183</v>
       </c>
@@ -27323,7 +27323,7 @@
       <c r="Y30" s="1"/>
       <c r="Z30" s="1"/>
     </row>
-    <row r="31" spans="1:26" ht="33.9" customHeight="1">
+    <row r="31" spans="1:26" ht="33.950000000000003" customHeight="1">
       <c r="A31" s="8" t="s">
         <v>185</v>
       </c>
@@ -32103,15 +32103,10 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100293B981485C9E24DAE651C97D9FBC267" ma:contentTypeVersion="3" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="81e1889baf096e0f1fabc7e628f510b3">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="32f33a6e-f018-4796-a6d6-b8c30f0661e9" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="4b8b816b6954550eb9ea5c593f5cc868" ns2:_="">
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100293B981485C9E24DAE651C97D9FBC267" ma:contentTypeVersion="9" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="73cbee31f6114801cea13732a9ec5387">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="32f33a6e-f018-4796-a6d6-b8c30f0661e9" xmlns:ns3="59ec22bb-74c1-4c3c-af96-122e757b18d2" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="4cc47ff3526632fc7ff348bab4cf07ac" ns2:_="" ns3:_="">
     <xsd:import namespace="32f33a6e-f018-4796-a6d6-b8c30f0661e9"/>
+    <xsd:import namespace="59ec22bb-74c1-4c3c-af96-122e757b18d2"/>
     <xsd:element name="properties">
       <xsd:complexType>
         <xsd:sequence>
@@ -32121,6 +32116,11 @@
                 <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
                 <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
                 <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
+                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
+                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
               </xsd:all>
             </xsd:complexType>
           </xsd:element>
@@ -32145,6 +32145,43 @@
       <xsd:simpleType>
         <xsd:restriction base="dms:Note"/>
       </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceDateTaken" ma:index="11" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceGenerationTime" ma:index="12" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceEventHashCode" ma:index="13" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="15" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="1374c586-51ca-419d-b13a-551147e70874" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="59ec22bb-74c1-4c3c-af96-122e757b18d2" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="TaxCatchAll" ma:index="16" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{281605ea-d3cc-4310-8c97-aa0e64c9f496}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="59ec22bb-74c1-4c3c-af96-122e757b18d2">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:MultiChoiceLookup">
+            <xsd:sequence>
+              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
     </xsd:element>
   </xsd:schema>
   <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
@@ -32246,7 +32283,7 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
@@ -32255,7 +32292,30 @@
 </FormTemplates>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="59ec22bb-74c1-4c3c-af96-122e757b18d2" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="32f33a6e-f018-4796-a6d6-b8c30f0661e9">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6DE437FB-03E2-4E33-8312-4C878C1580FC}"/>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F83B75D5-3426-4982-A846-B680B79A2C1B}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B78765EF-BFC8-412C-A3DC-565D32D6453C}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
@@ -32269,16 +32329,4 @@
     <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3AC5F987-5689-4E0E-BD79-08BDC8E05F2A}"/>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F83B75D5-3426-4982-A846-B680B79A2C1B}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/01-artefactos-de-gestao/01.06-avaliacao-interna-do-grupo/m2-mapa-carga-planeada-v01.xlsx
+++ b/01-artefactos-de-gestao/01.06-avaliacao-interna-do-grupo/m2-mapa-carga-planeada-v01.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ipppt.sharepoint.com/teams/LEI-GrupodeLDS-UTPORTO/Documentos Partilhados/projeto/01-artefactos-de-gestao/01.06-avaliacao-interna-do-grupo/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ipppt.sharepoint.com/teams/LEI-GrupodeLDS-UTPORTO/Documentos Partilhados/Para M2/Gestão/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="257" documentId="13_ncr:1_{36D489DA-0E1E-4AAB-A288-D8B9E481960E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0C810873-E560-4E71-AF03-410D895BB471}"/>
+  <xr:revisionPtr revIDLastSave="253" documentId="13_ncr:1_{36D489DA-0E1E-4AAB-A288-D8B9E481960E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1B17431A-9C2C-4B69-89A7-455B924E41A1}"/>
   <bookViews>
-    <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="16305" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="13056" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Mapa de Carga Planeada" sheetId="1" r:id="rId1"/>
@@ -839,6 +839,12 @@
     <t>/projeto/01-artefactos-de-gestao/01.04-backlog-de-projeto/m2-s02-sprint-backlog-v01.xlsx</t>
   </si>
   <si>
+    <t>/projeto/01-artefactos-de-gestao/01.03-reunioes-de-grupo/m1-20260919-s01-sprint-backlog-v01.pdf</t>
+  </si>
+  <si>
+    <t>/projeto/01-artefactos-de-gestao/01.03-reunioes-de-grupo/m2-20261002-s02-sprint-backlog-v01.pdf</t>
+  </si>
+  <si>
     <t>Atualizar Grelha de Rotação de Papéis</t>
   </si>
   <si>
@@ -879,12 +885,6 @@
   </si>
   <si>
     <t>/projeto/01-artefactos-de-gestao/01.03-reunioes-de-grupo/01.03.03-reunioes-de-sprint-planning/01.03.03.02-atas/m2-20261002-ata-sprint-planning-v01.pdf</t>
-  </si>
-  <si>
-    <t>/projeto/01-artefactos-de-gestao/01.04-backlog-de-projeto/m2-s02-20261007-sprint-backlog-v01.pdf</t>
-  </si>
-  <si>
-    <t>/projeto/01-artefactos-de-gestao/01.04-backlog-de-projeto/m1-20260919-s01-sprint-backlog-v01.pdf</t>
   </si>
 </sst>
 </file>
@@ -1476,10 +1476,10 @@
       <sheetName val="Listas de apoio"/>
     </sheetNames>
     <sheetDataSet>
-      <sheetData sheetId="0"/>
-      <sheetData sheetId="1"/>
-      <sheetData sheetId="2"/>
-      <sheetData sheetId="3"/>
+      <sheetData sheetId="0" refreshError="1"/>
+      <sheetData sheetId="1" refreshError="1"/>
+      <sheetData sheetId="2" refreshError="1"/>
+      <sheetData sheetId="3" refreshError="1"/>
       <sheetData sheetId="4">
         <row r="5">
           <cell r="A5">
@@ -1716,7 +1716,7 @@
     <tabColor rgb="FF1F4E78"/>
   </sheetPr>
   <dimension ref="A1:Z193"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="13.8"/>
   <cols>
     <col min="1" max="1" width="19" customWidth="1"/>
     <col min="2" max="5" width="17" customWidth="1"/>
@@ -1847,7 +1847,7 @@
       <c r="Y4" s="1"/>
       <c r="Z4" s="1"/>
     </row>
-    <row r="5" spans="1:26" ht="21.95" customHeight="1">
+    <row r="5" spans="1:26" ht="21.9" customHeight="1">
       <c r="A5" s="23" t="s">
         <v>4</v>
       </c>
@@ -2036,7 +2036,7 @@
       <c r="Y10" s="1"/>
       <c r="Z10" s="1"/>
     </row>
-    <row r="11" spans="1:26" ht="21.95" customHeight="1">
+    <row r="11" spans="1:26" ht="21.9" customHeight="1">
       <c r="A11" s="23" t="s">
         <v>10</v>
       </c>
@@ -2106,7 +2106,7 @@
       <c r="Y12" s="1"/>
       <c r="Z12" s="1"/>
     </row>
-    <row r="13" spans="1:26" ht="24">
+    <row r="13" spans="1:26" ht="22.8">
       <c r="A13" s="3" t="str">
         <f>IF('Listas de apoio'!G5="","",'Listas de apoio'!G5)</f>
         <v>André Filipe Moreira Mesquita</v>
@@ -2152,7 +2152,7 @@
       <c r="Y13" s="1"/>
       <c r="Z13" s="1"/>
     </row>
-    <row r="14" spans="1:26" ht="24">
+    <row r="14" spans="1:26" ht="22.8">
       <c r="A14" s="3" t="str">
         <f>IF('Listas de apoio'!G6="","",'Listas de apoio'!G6)</f>
         <v>Gonçalo Dinis Magalhães Teixeira</v>
@@ -2198,7 +2198,7 @@
       <c r="Y14" s="1"/>
       <c r="Z14" s="1"/>
     </row>
-    <row r="15" spans="1:26" ht="24">
+    <row r="15" spans="1:26">
       <c r="A15" s="3" t="str">
         <f>IF('Listas de apoio'!G7="","",'Listas de apoio'!G7)</f>
         <v>Gonçalo Magalhães Ribeiro</v>
@@ -2244,7 +2244,7 @@
       <c r="Y15" s="1"/>
       <c r="Z15" s="1"/>
     </row>
-    <row r="16" spans="1:26" ht="24">
+    <row r="16" spans="1:26">
       <c r="A16" s="3" t="str">
         <f>IF('Listas de apoio'!G8="","",'Listas de apoio'!G8)</f>
         <v>Ivan Cristiano Silva Mendes</v>
@@ -2363,7 +2363,7 @@
       <c r="Y18" s="1"/>
       <c r="Z18" s="1"/>
     </row>
-    <row r="19" spans="1:26" ht="21.95" customHeight="1">
+    <row r="19" spans="1:26" ht="21.9" customHeight="1">
       <c r="A19" s="23" t="s">
         <v>18</v>
       </c>
@@ -2651,7 +2651,7 @@
       <c r="Y27" s="1"/>
       <c r="Z27" s="1"/>
     </row>
-    <row r="28" spans="1:26" ht="21.95" customHeight="1">
+    <row r="28" spans="1:26" ht="21.9" customHeight="1">
       <c r="A28" s="23" t="s">
         <v>27</v>
       </c>
@@ -7825,17 +7825,17 @@
     <tabColor rgb="FF5B9BD5"/>
   </sheetPr>
   <dimension ref="A1:Z193"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="13.8"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
-    <col min="2" max="2" width="30.25" customWidth="1"/>
+    <col min="2" max="2" width="30.19921875" customWidth="1"/>
     <col min="3" max="3" width="42" customWidth="1"/>
     <col min="4" max="4" width="18" customWidth="1"/>
-    <col min="5" max="5" width="29.375" customWidth="1"/>
+    <col min="5" max="5" width="29.3984375" customWidth="1"/>
     <col min="6" max="6" width="11" customWidth="1"/>
-    <col min="7" max="7" width="28.125" customWidth="1"/>
+    <col min="7" max="7" width="28.09765625" customWidth="1"/>
     <col min="8" max="8" width="11" customWidth="1"/>
-    <col min="9" max="9" width="29.375" customWidth="1"/>
+    <col min="9" max="9" width="29.3984375" customWidth="1"/>
     <col min="10" max="10" width="11" customWidth="1"/>
   </cols>
   <sheetData>
@@ -7961,7 +7961,7 @@
       <c r="Y4" s="1"/>
       <c r="Z4" s="1"/>
     </row>
-    <row r="5" spans="1:26" ht="21.95" customHeight="1">
+    <row r="5" spans="1:26" ht="21.9" customHeight="1">
       <c r="A5" s="23" t="s">
         <v>36</v>
       </c>
@@ -8025,7 +8025,7 @@
       <c r="Y6" s="1"/>
       <c r="Z6" s="1"/>
     </row>
-    <row r="7" spans="1:26" ht="16.899999999999999" customHeight="1">
+    <row r="7" spans="1:26" ht="16.8" customHeight="1">
       <c r="A7" s="4" t="s">
         <v>155</v>
       </c>
@@ -8681,7 +8681,7 @@
       <c r="Y27" s="1"/>
       <c r="Z27" s="1"/>
     </row>
-    <row r="28" spans="1:26" ht="21.95" customHeight="1">
+    <row r="28" spans="1:26" ht="21.9" customHeight="1">
       <c r="A28" s="23" t="s">
         <v>41</v>
       </c>
@@ -8711,7 +8711,7 @@
       <c r="Y28" s="1"/>
       <c r="Z28" s="1"/>
     </row>
-    <row r="29" spans="1:26" ht="39.950000000000003" customHeight="1">
+    <row r="29" spans="1:26" ht="39.9" customHeight="1">
       <c r="A29" s="2" t="s">
         <v>28</v>
       </c>
@@ -8757,7 +8757,7 @@
       <c r="C30" s="29"/>
       <c r="D30" s="29"/>
       <c r="E30" s="29" t="s">
-        <v>271</v>
+        <v>256</v>
       </c>
       <c r="F30" s="29"/>
       <c r="G30" s="29"/>
@@ -8793,12 +8793,12 @@
       <c r="C31" s="29"/>
       <c r="D31" s="29"/>
       <c r="E31" s="29" t="s">
-        <v>270</v>
+        <v>257</v>
       </c>
       <c r="F31" s="29"/>
       <c r="G31" s="29"/>
       <c r="H31" s="29" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="I31" s="29"/>
       <c r="J31" s="29"/>
@@ -9351,7 +9351,7 @@
       <c r="Y50" s="1"/>
       <c r="Z50" s="1"/>
     </row>
-    <row r="51" spans="1:26" ht="21.95" customHeight="1">
+    <row r="51" spans="1:26" ht="21.9" customHeight="1">
       <c r="A51" s="23" t="s">
         <v>44</v>
       </c>
@@ -9976,7 +9976,7 @@
         <v>242</v>
       </c>
       <c r="C64" s="18" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="D64" s="20">
         <v>10</v>
@@ -10078,7 +10078,7 @@
         <v>244</v>
       </c>
       <c r="C66" s="18" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="D66" s="20">
         <v>30</v>
@@ -10129,7 +10129,7 @@
         <v>245</v>
       </c>
       <c r="C67" s="18" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="D67" s="20">
         <v>30</v>
@@ -10231,7 +10231,7 @@
         <v>247</v>
       </c>
       <c r="C69" s="18" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D69" s="20">
         <v>50</v>
@@ -10384,7 +10384,7 @@
         <v>250</v>
       </c>
       <c r="C72" s="18" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="D72" s="20">
         <v>50</v>
@@ -10432,10 +10432,10 @@
         <v>157</v>
       </c>
       <c r="B73" s="18" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="C73" s="18" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D73" s="20">
         <v>30</v>
@@ -10483,10 +10483,10 @@
         <v>157</v>
       </c>
       <c r="B74" s="18" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="C74" s="19" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="D74" s="20">
         <v>30</v>
@@ -10534,10 +10534,10 @@
         <v>157</v>
       </c>
       <c r="B75" s="18" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="C75" s="19" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="D75" s="20">
         <v>20</v>
@@ -10585,10 +10585,10 @@
         <v>157</v>
       </c>
       <c r="B76" s="18" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="C76" s="18" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="D76" s="20">
         <v>20</v>
@@ -14676,7 +14676,7 @@
     <tabColor rgb="FFA5A5A5"/>
   </sheetPr>
   <dimension ref="A1:Z200"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="13.8"/>
   <cols>
     <col min="1" max="1" width="43" customWidth="1"/>
     <col min="2" max="2" width="16" customWidth="1"/>
@@ -14808,7 +14808,7 @@
       <c r="Y4" s="1"/>
       <c r="Z4" s="1"/>
     </row>
-    <row r="5" spans="1:26" ht="33.950000000000003" customHeight="1">
+    <row r="5" spans="1:26" ht="33.9" customHeight="1">
       <c r="A5" s="3" t="s">
         <v>60</v>
       </c>
@@ -14845,7 +14845,7 @@
       <c r="Y5" s="1"/>
       <c r="Z5" s="1"/>
     </row>
-    <row r="6" spans="1:26" ht="33.950000000000003" customHeight="1">
+    <row r="6" spans="1:26" ht="33.9" customHeight="1">
       <c r="A6" s="3" t="s">
         <v>63</v>
       </c>
@@ -14882,7 +14882,7 @@
       <c r="Y6" s="1"/>
       <c r="Z6" s="1"/>
     </row>
-    <row r="7" spans="1:26" ht="33.950000000000003" customHeight="1">
+    <row r="7" spans="1:26" ht="33.9" customHeight="1">
       <c r="A7" s="3" t="s">
         <v>65</v>
       </c>
@@ -14919,7 +14919,7 @@
       <c r="Y7" s="1"/>
       <c r="Z7" s="1"/>
     </row>
-    <row r="8" spans="1:26" ht="33.950000000000003" customHeight="1">
+    <row r="8" spans="1:26" ht="33.9" customHeight="1">
       <c r="A8" s="3" t="s">
         <v>67</v>
       </c>
@@ -14957,7 +14957,7 @@
       <c r="Y8" s="1"/>
       <c r="Z8" s="1"/>
     </row>
-    <row r="9" spans="1:26" ht="33.950000000000003" customHeight="1">
+    <row r="9" spans="1:26" ht="33.9" customHeight="1">
       <c r="A9" s="3" t="s">
         <v>69</v>
       </c>
@@ -14995,7 +14995,7 @@
       <c r="Y9" s="1"/>
       <c r="Z9" s="1"/>
     </row>
-    <row r="10" spans="1:26" ht="33.950000000000003" customHeight="1">
+    <row r="10" spans="1:26" ht="33.9" customHeight="1">
       <c r="A10" s="3" t="s">
         <v>208</v>
       </c>
@@ -15033,7 +15033,7 @@
       <c r="Y10" s="1"/>
       <c r="Z10" s="1"/>
     </row>
-    <row r="11" spans="1:26" ht="33.950000000000003" customHeight="1">
+    <row r="11" spans="1:26" ht="33.9" customHeight="1">
       <c r="A11" s="3" t="s">
         <v>72</v>
       </c>
@@ -15071,7 +15071,7 @@
       <c r="Y11" s="1"/>
       <c r="Z11" s="1"/>
     </row>
-    <row r="12" spans="1:26" ht="33.950000000000003" customHeight="1">
+    <row r="12" spans="1:26" ht="33.9" customHeight="1">
       <c r="A12" s="3" t="s">
         <v>74</v>
       </c>
@@ -15109,7 +15109,7 @@
       <c r="Y12" s="1"/>
       <c r="Z12" s="1"/>
     </row>
-    <row r="13" spans="1:26" ht="33.950000000000003" customHeight="1">
+    <row r="13" spans="1:26" ht="33.9" customHeight="1">
       <c r="A13" s="3" t="s">
         <v>76</v>
       </c>
@@ -15147,7 +15147,7 @@
       <c r="Y13" s="1"/>
       <c r="Z13" s="1"/>
     </row>
-    <row r="14" spans="1:26" ht="33.950000000000003" customHeight="1">
+    <row r="14" spans="1:26" ht="33.9" customHeight="1">
       <c r="A14" s="3" t="s">
         <v>78</v>
       </c>
@@ -15185,7 +15185,7 @@
       <c r="Y14" s="1"/>
       <c r="Z14" s="1"/>
     </row>
-    <row r="15" spans="1:26" ht="33.950000000000003" customHeight="1">
+    <row r="15" spans="1:26" ht="33.9" customHeight="1">
       <c r="A15" s="3" t="s">
         <v>80</v>
       </c>
@@ -15223,7 +15223,7 @@
       <c r="Y15" s="1"/>
       <c r="Z15" s="1"/>
     </row>
-    <row r="16" spans="1:26" ht="33.950000000000003" customHeight="1">
+    <row r="16" spans="1:26" ht="33.9" customHeight="1">
       <c r="A16" s="3" t="s">
         <v>187</v>
       </c>
@@ -15261,7 +15261,7 @@
       <c r="Y16" s="1"/>
       <c r="Z16" s="1"/>
     </row>
-    <row r="17" spans="1:26" ht="33.950000000000003" customHeight="1">
+    <row r="17" spans="1:26" ht="33.9" customHeight="1">
       <c r="A17" s="3" t="s">
         <v>82</v>
       </c>
@@ -15299,7 +15299,7 @@
       <c r="Y17" s="1"/>
       <c r="Z17" s="1"/>
     </row>
-    <row r="18" spans="1:26" ht="33.950000000000003" customHeight="1">
+    <row r="18" spans="1:26" ht="33.9" customHeight="1">
       <c r="A18" s="3" t="s">
         <v>84</v>
       </c>
@@ -15337,7 +15337,7 @@
       <c r="Y18" s="1"/>
       <c r="Z18" s="1"/>
     </row>
-    <row r="19" spans="1:26" ht="33.950000000000003" customHeight="1">
+    <row r="19" spans="1:26" ht="33.9" customHeight="1">
       <c r="A19" s="3" t="s">
         <v>86</v>
       </c>
@@ -15375,7 +15375,7 @@
       <c r="Y19" s="1"/>
       <c r="Z19" s="1"/>
     </row>
-    <row r="20" spans="1:26" ht="33.950000000000003" customHeight="1">
+    <row r="20" spans="1:26" ht="33.9" customHeight="1">
       <c r="A20" s="3" t="s">
         <v>88</v>
       </c>
@@ -15413,7 +15413,7 @@
       <c r="Y20" s="1"/>
       <c r="Z20" s="1"/>
     </row>
-    <row r="21" spans="1:26" ht="33.950000000000003" customHeight="1">
+    <row r="21" spans="1:26" ht="33.9" customHeight="1">
       <c r="A21" s="3" t="s">
         <v>189</v>
       </c>
@@ -15451,7 +15451,7 @@
       <c r="Y21" s="1"/>
       <c r="Z21" s="1"/>
     </row>
-    <row r="22" spans="1:26" ht="33.950000000000003" customHeight="1">
+    <row r="22" spans="1:26" ht="33.9" customHeight="1">
       <c r="A22" s="3" t="s">
         <v>191</v>
       </c>
@@ -15489,7 +15489,7 @@
       <c r="Y22" s="1"/>
       <c r="Z22" s="1"/>
     </row>
-    <row r="23" spans="1:26" ht="33.950000000000003" customHeight="1">
+    <row r="23" spans="1:26" ht="33.9" customHeight="1">
       <c r="A23" s="3" t="s">
         <v>193</v>
       </c>
@@ -15527,7 +15527,7 @@
       <c r="Y23" s="1"/>
       <c r="Z23" s="1"/>
     </row>
-    <row r="24" spans="1:26" ht="33.950000000000003" customHeight="1">
+    <row r="24" spans="1:26" ht="33.9" customHeight="1">
       <c r="A24" s="3" t="s">
         <v>195</v>
       </c>
@@ -15565,7 +15565,7 @@
       <c r="Y24" s="1"/>
       <c r="Z24" s="1"/>
     </row>
-    <row r="25" spans="1:26" ht="33.950000000000003" customHeight="1">
+    <row r="25" spans="1:26" ht="33.9" customHeight="1">
       <c r="A25" s="3" t="s">
         <v>197</v>
       </c>
@@ -15603,7 +15603,7 @@
       <c r="Y25" s="1"/>
       <c r="Z25" s="1"/>
     </row>
-    <row r="26" spans="1:26" ht="33.950000000000003" customHeight="1">
+    <row r="26" spans="1:26" ht="33.9" customHeight="1">
       <c r="A26" s="3" t="s">
         <v>198</v>
       </c>
@@ -15641,7 +15641,7 @@
       <c r="Y26" s="1"/>
       <c r="Z26" s="1"/>
     </row>
-    <row r="27" spans="1:26" ht="33.950000000000003" customHeight="1">
+    <row r="27" spans="1:26" ht="33.9" customHeight="1">
       <c r="A27" s="3" t="s">
         <v>200</v>
       </c>
@@ -15679,7 +15679,7 @@
       <c r="Y27" s="1"/>
       <c r="Z27" s="1"/>
     </row>
-    <row r="28" spans="1:26" ht="33.950000000000003" customHeight="1">
+    <row r="28" spans="1:26" ht="33.9" customHeight="1">
       <c r="A28" s="3" t="s">
         <v>202</v>
       </c>
@@ -15717,7 +15717,7 @@
       <c r="Y28" s="1"/>
       <c r="Z28" s="1"/>
     </row>
-    <row r="29" spans="1:26" ht="33.950000000000003" customHeight="1">
+    <row r="29" spans="1:26" ht="33.9" customHeight="1">
       <c r="A29" s="3" t="s">
         <v>90</v>
       </c>
@@ -15755,7 +15755,7 @@
       <c r="Y29" s="1"/>
       <c r="Z29" s="1"/>
     </row>
-    <row r="30" spans="1:26" ht="33.950000000000003" customHeight="1">
+    <row r="30" spans="1:26" ht="33.9" customHeight="1">
       <c r="A30" s="3" t="s">
         <v>92</v>
       </c>
@@ -20573,7 +20573,7 @@
     <tabColor rgb="FF70AD47"/>
   </sheetPr>
   <dimension ref="A1:Z200"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="13.8"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
     <col min="2" max="2" width="27" customWidth="1"/>
@@ -20677,7 +20677,7 @@
       <c r="Y3" s="1"/>
       <c r="Z3" s="1"/>
     </row>
-    <row r="4" spans="1:26" ht="60">
+    <row r="4" spans="1:26" ht="57">
       <c r="A4" s="3">
         <v>1</v>
       </c>
@@ -21101,7 +21101,7 @@
       <c r="Y15" s="1"/>
       <c r="Z15" s="1"/>
     </row>
-    <row r="16" spans="1:26" ht="21.95" customHeight="1">
+    <row r="16" spans="1:26" ht="21.9" customHeight="1">
       <c r="A16" s="23" t="s">
         <v>128</v>
       </c>
@@ -26349,7 +26349,7 @@
     <tabColor rgb="FFA5A5A5"/>
   </sheetPr>
   <dimension ref="A1:Z200"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="13.8"/>
   <cols>
     <col min="1" max="1" width="19" customWidth="1"/>
     <col min="2" max="2" width="3" customWidth="1"/>
@@ -26491,7 +26491,7 @@
       <c r="Y4" s="1"/>
       <c r="Z4" s="1"/>
     </row>
-    <row r="5" spans="1:26" ht="24">
+    <row r="5" spans="1:26" ht="22.8">
       <c r="A5" s="3">
         <v>10</v>
       </c>
@@ -26531,7 +26531,7 @@
       <c r="Y5" s="1"/>
       <c r="Z5" s="1"/>
     </row>
-    <row r="6" spans="1:26" ht="24">
+    <row r="6" spans="1:26" ht="22.8">
       <c r="A6" s="3">
         <v>20</v>
       </c>
@@ -26571,7 +26571,7 @@
       <c r="Y6" s="1"/>
       <c r="Z6" s="1"/>
     </row>
-    <row r="7" spans="1:26" ht="24">
+    <row r="7" spans="1:26" ht="22.8">
       <c r="A7" s="3">
         <v>30</v>
       </c>
@@ -26611,7 +26611,7 @@
       <c r="Y7" s="1"/>
       <c r="Z7" s="1"/>
     </row>
-    <row r="8" spans="1:26" ht="24">
+    <row r="8" spans="1:26" ht="22.8">
       <c r="A8" s="3">
         <v>50</v>
       </c>
@@ -27165,7 +27165,7 @@
       <c r="Y25" s="1"/>
       <c r="Z25" s="1"/>
     </row>
-    <row r="26" spans="1:26" ht="21.95" customHeight="1">
+    <row r="26" spans="1:26" ht="21.9" customHeight="1">
       <c r="A26" s="23" t="s">
         <v>178</v>
       </c>
@@ -27195,7 +27195,7 @@
       <c r="Y26" s="1"/>
       <c r="Z26" s="1"/>
     </row>
-    <row r="27" spans="1:26" ht="33.950000000000003" customHeight="1">
+    <row r="27" spans="1:26" ht="33.9" customHeight="1">
       <c r="A27" s="8" t="s">
         <v>151</v>
       </c>
@@ -27227,7 +27227,7 @@
       <c r="Y27" s="1"/>
       <c r="Z27" s="1"/>
     </row>
-    <row r="28" spans="1:26" ht="33.950000000000003" customHeight="1">
+    <row r="28" spans="1:26" ht="33.9" customHeight="1">
       <c r="A28" s="8" t="s">
         <v>179</v>
       </c>
@@ -27259,7 +27259,7 @@
       <c r="Y28" s="1"/>
       <c r="Z28" s="1"/>
     </row>
-    <row r="29" spans="1:26" ht="33.950000000000003" customHeight="1">
+    <row r="29" spans="1:26" ht="33.9" customHeight="1">
       <c r="A29" s="8" t="s">
         <v>181</v>
       </c>
@@ -27291,7 +27291,7 @@
       <c r="Y29" s="1"/>
       <c r="Z29" s="1"/>
     </row>
-    <row r="30" spans="1:26" ht="33.950000000000003" customHeight="1">
+    <row r="30" spans="1:26" ht="33.9" customHeight="1">
       <c r="A30" s="8" t="s">
         <v>183</v>
       </c>
@@ -27323,7 +27323,7 @@
       <c r="Y30" s="1"/>
       <c r="Z30" s="1"/>
     </row>
-    <row r="31" spans="1:26" ht="33.950000000000003" customHeight="1">
+    <row r="31" spans="1:26" ht="33.9" customHeight="1">
       <c r="A31" s="8" t="s">
         <v>185</v>
       </c>
@@ -32103,10 +32103,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100293B981485C9E24DAE651C97D9FBC267" ma:contentTypeVersion="9" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="73cbee31f6114801cea13732a9ec5387">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="32f33a6e-f018-4796-a6d6-b8c30f0661e9" xmlns:ns3="59ec22bb-74c1-4c3c-af96-122e757b18d2" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="4cc47ff3526632fc7ff348bab4cf07ac" ns2:_="" ns3:_="">
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100293B981485C9E24DAE651C97D9FBC267" ma:contentTypeVersion="3" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="81e1889baf096e0f1fabc7e628f510b3">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="32f33a6e-f018-4796-a6d6-b8c30f0661e9" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="4b8b816b6954550eb9ea5c593f5cc868" ns2:_="">
     <xsd:import namespace="32f33a6e-f018-4796-a6d6-b8c30f0661e9"/>
-    <xsd:import namespace="59ec22bb-74c1-4c3c-af96-122e757b18d2"/>
     <xsd:element name="properties">
       <xsd:complexType>
         <xsd:sequence>
@@ -32116,11 +32121,6 @@
                 <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
                 <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
                 <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
-                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
-                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
               </xsd:all>
             </xsd:complexType>
           </xsd:element>
@@ -32145,43 +32145,6 @@
       <xsd:simpleType>
         <xsd:restriction base="dms:Note"/>
       </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceDateTaken" ma:index="11" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceGenerationTime" ma:index="12" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceEventHashCode" ma:index="13" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="15" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="1374c586-51ca-419d-b13a-551147e70874" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="59ec22bb-74c1-4c3c-af96-122e757b18d2" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="TaxCatchAll" ma:index="16" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{281605ea-d3cc-4310-8c97-aa0e64c9f496}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="59ec22bb-74c1-4c3c-af96-122e757b18d2">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:MultiChoiceLookup">
-            <xsd:sequence>
-              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
     </xsd:element>
   </xsd:schema>
   <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
@@ -32283,7 +32246,7 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
@@ -32292,30 +32255,7 @@
 </FormTemplates>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="59ec22bb-74c1-4c3c-af96-122e757b18d2" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="32f33a6e-f018-4796-a6d6-b8c30f0661e9">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6DE437FB-03E2-4E33-8312-4C878C1580FC}"/>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F83B75D5-3426-4982-A846-B680B79A2C1B}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B78765EF-BFC8-412C-A3DC-565D32D6453C}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
@@ -32329,4 +32269,16 @@
     <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3AC5F987-5689-4E0E-BD79-08BDC8E05F2A}"/>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F83B75D5-3426-4982-A846-B680B79A2C1B}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>